--- a/results/job_matches_2026-10-09.xlsx
+++ b/results/job_matches_2026-10-09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,17 +526,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Alvaria</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,24 +554,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0aa6dd1b04fbce5</t>
+          <t>https://www.indeed.com/viewjob?jk=39485b7b1b648afd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>World Bank Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,24 +589,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3c1554c10248b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b0aa6dd1b04fbce5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alvaria</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39485b7b1b648afd</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3c1554c10248b1</t>
         </is>
       </c>
     </row>
@@ -666,52 +666,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Slalom Flex (Project Based)- ML Ops Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Albany, NY, USA USA</t>
+          <t>Westlake, TX, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, ELT</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e0624b44a35626</t>
+          <t>https://www.indeed.com/viewjob?jk=c90944751a08861f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Leawood, KS, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,67 +729,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5dc654cacc73fe</t>
+          <t>https://www.indeed.com/viewjob?jk=803b407aed33b34c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>B1 - AI Platform Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Westlake, TX, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Spark, Kafka, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90944751a08861f</t>
+          <t>https://www.indeed.com/viewjob?jk=a26f6d29c9750839</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cloud Infrastructure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Kansas City, MO, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,67 +799,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803b407aed33b34c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a2d2e8f143d7289</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>FTS Network Services – Data Analytics Advisor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Snowflake, dbt, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21725d4d5a969dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=39867fe787e05360</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Oaks, PA, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Databricks, Spark, PySpark, Scala, Kafka, PostgreSQL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=415b6d66e75228d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8210b0e233986964</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kansas City, MO, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a2d2e8f143d7289</t>
+          <t>https://www.indeed.com/viewjob?jk=941ac528d3de9bd2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Engineer Consultant</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>St. Louis, MO, USA USA</t>
+          <t>Denver, CO, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,42 +929,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d8a4cf8d1aaf1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0696223bbad4f3b2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oaks, PA, USA USA</t>
+          <t>Brentwood, TN, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,32 +974,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8210b0e233986964</t>
+          <t>https://www.indeed.com/viewjob?jk=52c9a93606e8b426</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>engineer sr - ST (Hybrid) Seattle WA</t>
+          <t>Sr. Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=679a365e45ca5a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a650bae5ce2865af</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Schaumburg, IL, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,19 +1044,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941ac528d3de9bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1830ef2a37b276</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1065,46 +1065,46 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0696223bbad4f3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7b919d7fa31ebc26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AJAY K- SOLUTION ARCHITECT | CLOUD, DATA, INTEGRATION &amp; AI-ENABLED PLATFORMS.</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cassco International, Inc</t>
+          <t>Shift4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, ECS, IAM, Scala, Polars, Snowflake, Time Travel, dbt, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9af1985824c8bc86</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6edb1d735ef07e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Shift4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brentwood, TN, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, Scala, Polars, Snowflake, Time Travel, dbt, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c9a93606e8b426</t>
+          <t>https://www.indeed.com/viewjob?jk=d034225cfcd8edfb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Azure Data Engineer with Databricks</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Alvaria</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,67 +1184,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a650bae5ce2865af</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb0737b251a7eee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>B2/C1 - AI Engineer 4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Shift4</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, Polars, Snowflake, Time Travel, dbt, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6edb1d735ef07e</t>
+          <t>https://www.indeed.com/viewjob?jk=d91279c1d35293f9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, S3, RDS, Azure, Data Lake Storage, Snowflake, Time Travel, Zero-Copy Cloning, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b919d7fa31ebc26</t>
+          <t>https://www.indeed.com/viewjob?jk=99485071e09ba5d9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, USA USA</t>
+          <t>Sterling, VA, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,32 +1289,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1830ef2a37b276</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbfc9f6705769bd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer I (Data Pipelines)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alvaria</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb0737b251a7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=77f88462ba46b951</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I (Data Pipelines)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,24 +1359,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f88462ba46b951</t>
+          <t>https://www.indeed.com/viewjob?jk=7aec8d989d23632c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aec8d989d23632c</t>
+          <t>https://www.indeed.com/viewjob?jk=3eca95f7972c478d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>B2/C1 - AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,42 +1419,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Lake Storage, Snowflake, Time Travel, Zero-Copy Cloning, Data Modeling, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99485071e09ba5d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9e428958ad9e8a14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer (Seattle)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sterling, VA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,19 +1464,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbfc9f6705769bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ef35c3d0ab2f06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Staritas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1485,46 +1485,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eca95f7972c478d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc03dc2d2fb3968d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DBA II</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,32 +1534,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa3a48755605f28e</t>
+          <t>https://www.indeed.com/viewjob?jk=63d4e3867310a550</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DBA II</t>
+          <t>ETDP Associate - Data Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acdebbbdc22b8477</t>
+          <t>https://www.indeed.com/viewjob?jk=cc612453c81627d3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Seattle)</t>
+          <t>Advisor-Data Engineer MDM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Memphis, TN, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ef35c3d0ab2f06</t>
+          <t>https://www.indeed.com/viewjob?jk=efe237925fb7924c</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1646,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>ETL Engineer - Hybrid (Atlanta, GA)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d4e3867310a550</t>
+          <t>https://www.indeed.com/viewjob?jk=7f025291341db017</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Advisor-Data Engineer MDM</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FedEx Freight</t>
+          <t>WorkWave™</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Memphis, TN, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,34 +1699,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57eec5ffd5808ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e0631f3e16004ff9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Advisor-Data Engineer MDM</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FedEx Freight</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Memphis, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1744,24 +1744,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe237925fb7924c</t>
+          <t>https://www.indeed.com/viewjob?jk=f563024b3edfa1e7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ETDP Associate - Data Analytics</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc612453c81627d3</t>
+          <t>https://www.indeed.com/viewjob?jk=76d8be6b3de911a3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Engineer – ReactJS / Python / SQL Server</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>Foresight IT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,34 +1804,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>S3, API Gateway, Azure, Scala, SQL Server, Data Modeling, REST API integration, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0631f3e16004ff9</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab9dc0adc464b1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data &amp; Analytics Developer II - Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wet Coast Logistics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Greenville, SC, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, ETL, Power BI, MLOps, MLflow, pytest</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f563024b3edfa1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4930ffb452c6e901</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Quality Engineer - E2E Testing</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d8be6b3de911a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f74b13b92fba8065</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – ReactJS / Python / SQL Server</t>
+          <t>Development Security Operations (DevSecOps) Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Foresight IT</t>
+          <t>AEG Worldwide</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,42 +1909,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S3, API Gateway, Azure, Scala, SQL Server, Data Modeling, REST API integration, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab9dc0adc464b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1e4327cd6468ba</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Developer II - Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wet Coast Logistics</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Greenville, SC, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, ETL, Power BI, MLOps, MLflow, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,32 +1954,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930ffb452c6e901</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b039efd1bdf1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Quality Engineer - E2E Testing</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Naviga Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f74b13b92fba8065</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2a21fac0f0100e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (SQL Server DBA)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Curant Health Georgia LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, USA USA</t>
+          <t>Smyrna, GA, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,32 +2024,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f393fa8d32e16893</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f2fb1b8f4b0f0b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Development Security Operations (DevSecOps) Engineer</t>
+          <t>Senior Engineer, Data Services</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AEG Worldwide</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1e4327cd6468ba</t>
+          <t>https://www.indeed.com/viewjob?jk=51dae1964caf1fbb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Services</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dae1964caf1fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=abce2386bdc64e52</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>BAM Technologies, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b039efd1bdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=12b4ba48e48f905c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Python Developer w/d banking domain Exp in Jersey City, NJ – 5 Days Onsite</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Curant Health Georgia LLC</t>
+          <t>SGN Global Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Smyrna, GA, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f2fb1b8f4b0f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e855da5922ac48</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Naviga Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,34 +2189,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2a21fac0f0100e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b69cb4c0ab9836b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Developer III</t>
+          <t>Enterprise Cloud Architect (AWS)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BAM Technologies, LLC</t>
+          <t>Norfolk Southern</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,34 +2224,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b4ba48e48f905c</t>
+          <t>https://www.indeed.com/viewjob?jk=014160cc6df2ce6d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Digital Banking Full Stack Engineer</t>
+          <t>AI/ML DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>First Tech Federal Credit Union</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chelmsford, MA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,77 +2259,77 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a5dfa62a0d990</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fcf0f91468d631</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Python Developer w/d banking domain Exp in Jersey City, NJ – 5 Days Onsite</t>
+          <t>Full-Stack Engineer 4 (Python, React, AWS)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SGN Global Technologies</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e855da5922ac48</t>
+          <t>https://www.indeed.com/viewjob?jk=62a73708df2af64b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/ML DevOps Engineer</t>
+          <t>Full-stack Engineer 4 (Python/AWS)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fcf0f91468d631</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f16cbf818d2cc7</t>
         </is>
       </c>
     </row>
@@ -2451,17 +2451,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Integration Engineer 4</t>
+          <t>Mid-Level Snowflake Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, RDS, Azure, GCP, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Cloud Storage, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00c18c2f7ae91a00</t>
+          <t>https://www.indeed.com/viewjob?jk=efa77e320b69a5d6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mid-Level Snowflake Developer</t>
+          <t>Software Engineer, Core Platforms</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Cloud Storage, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,24 +2514,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa77e320b69a5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c10cdbcee7e892fd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Platforms</t>
+          <t>Azure Databricks architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>RM SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10cdbcee7e892fd</t>
+          <t>https://www.indeed.com/viewjob?jk=84d787c2acfd2551</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Databricks architect</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RM SOLUTIONS INC</t>
+          <t>Mindbody</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Azure, Scala, SQL Server, PostgreSQL, MongoDB, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,19 +2584,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d787c2acfd2551</t>
+          <t>https://www.indeed.com/viewjob?jk=3f824146c3510fa4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mindbody</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, SQL Server, PostgreSQL, MongoDB, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Power BI, Tableau, MLOps, MLflow, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f824146c3510fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a11006b13bb999b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Production Engineer - Realtime Products</t>
+          <t>Cyber Security Engineer-Application Security Tooling (SCA/SAST/ DAST/ MAST/ API Security)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,29 +2644,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, PostgreSQL, Terraform, Kubernetes</t>
+          <t>RDS, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75f442e4703aad</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ed5a614020b926</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Power BI, Tableau, MLOps, MLflow, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,67 +2689,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a11006b13bb999b</t>
+          <t>https://www.indeed.com/viewjob?jk=3e910c2a9db14c45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Milpitas, CA, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, YARN, Scala, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e910c2a9db14c45</t>
+          <t>https://www.indeed.com/viewjob?jk=eb578f07aff6f110</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Solutions Architect (Data)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MO, USA USA</t>
+          <t>Newport Beach, CA, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,32 +2759,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c96a2380ee98e7</t>
+          <t>https://www.indeed.com/viewjob?jk=145ea1e85469e08e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Tech-BAIN Service Reliability Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Universal Music Group</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, USA USA</t>
+          <t>Willow Grove, PA, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b959e0e3c13d4ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=113b0ef7bbd43b1b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, USA USA</t>
+          <t>Lemont, IL, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,34 +2819,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145ea1e85469e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=0c58980479804216</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Willow Grove, PA, USA USA</t>
+          <t>Oklahoma City, OK, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2864,24 +2864,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113b0ef7bbd43b1b</t>
+          <t>https://www.indeed.com/viewjob?jk=03d377e0f22b50c9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Liberty company insurance brokers</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, USA USA</t>
+          <t>Woodland Hills, CA, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,24 +2899,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d377e0f22b50c9</t>
+          <t>https://www.indeed.com/viewjob?jk=6cea5cc81a279b30</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Liberty company insurance brokers</t>
+          <t>Enable Dental</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,24 +2934,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cea5cc81a279b30</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b35f71127e713c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12 Elements Consulting</t>
+          <t>Surge InfoTech LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Alexandria, VA, USA USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,24 +2969,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961c09494cecca9b</t>
+          <t>https://www.indeed.com/viewjob?jk=009031cd529e79e4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Data &amp; Integrations Engineering)</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cedar INC</t>
+          <t>12 Elements Consulting</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Kafka, Snowflake, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a64073f77de1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=961c09494cecca9b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Enable Dental</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Research Triangle Park, NC, USA USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3029,34 +3029,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Snowflake, Oracle, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b35f71127e713c</t>
+          <t>https://www.indeed.com/viewjob?jk=703acd54a03be894</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Full Stack Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Surge InfoTech LLC</t>
+          <t>Medpro systems</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alexandria, VA, USA USA</t>
+          <t>Mount Arlington, NJ, USA USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009031cd529e79e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4711747a7e234c3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DataBricks Engineer</t>
+          <t>Enterprise Software Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NomiSo</t>
+          <t>Dartmouth College</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, USA USA</t>
+          <t>Hanover, NH, USA USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,24 +3109,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7372a5249c25b1</t>
+          <t>https://www.indeed.com/viewjob?jk=147e1a8f49587d0f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Engineer II</t>
+          <t>VIE - Software Engineer (based in Miami)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Medpro systems</t>
+          <t>Pelico</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mount Arlington, NJ, USA USA</t>
+          <t>Miami, FL, USA USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3144,24 +3144,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4711747a7e234c3</t>
+          <t>https://www.indeed.com/viewjob?jk=85b64e32ec1fb240</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Enterprise Software Engineer II</t>
+          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dartmouth College</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hanover, NH, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3179,24 +3179,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147e1a8f49587d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=68f0e55cdb56404f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Scala, ELT, MLOps, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b64e32ec1fb240</t>
+          <t>https://www.indeed.com/viewjob?jk=96a354be84c2774c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>.NET / PostgreSQL Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Strategic Operational Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,34 +3239,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, Scala, PostgreSQL, ETL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa47a8ff9ab65e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=4942ca1d88558983</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Microsoft Dynamics 365 F&amp;O Data Architect</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Innova Software Services</t>
+          <t>Strategic Operational Solutions</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,24 +3284,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b94a3a4f9e025c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa47a8ff9ab65e1a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
+          <t>Senior Automation Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Santa Ana, CA, USA USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,85 +3309,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68f0e55cdb56404f</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Reston, VA, USA USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, ELT, MLOps, MLflow, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96a354be84c2774c</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Automation Developer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Orange County's Credit Union</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Santa Ana, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed32f5ec4264db1b</t>
         </is>

--- a/results/job_matches_2026-10-09.xlsx
+++ b/results/job_matches_2026-10-09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,17 +491,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Magento Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,42 +509,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a263552cfd74efb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b8dc6eea200704fa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Magento Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alvaria</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39485b7b1b648afd</t>
+          <t>https://www.indeed.com/viewjob?jk=a263552cfd74efb4</t>
         </is>
       </c>
     </row>
@@ -596,17 +596,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Alvaria</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3c1554c10248b1</t>
+          <t>https://www.indeed.com/viewjob?jk=39485b7b1b648afd</t>
         </is>
       </c>
     </row>
@@ -806,17 +806,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FTS Network Services – Data Analytics Advisor</t>
+          <t>Senior Consultant - Data Platforms - REMOTE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Fortified Data</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39867fe787e05360</t>
+          <t>https://www.indeed.com/viewjob?jk=73378029918e0cc3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oaks, PA, USA USA</t>
+          <t>Hialeah, FL, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,34 +859,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Oracle, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8210b0e233986964</t>
+          <t>https://www.indeed.com/viewjob?jk=ecf219ffd88edd6e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>FTS Network Services – Data Analytics Advisor</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,34 +894,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941ac528d3de9bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=39867fe787e05360</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Oaks, PA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,42 +929,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0696223bbad4f3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8210b0e233986964</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brentwood, TN, USA USA</t>
+          <t>Irvine, CA, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,49 +974,49 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c9a93606e8b426</t>
+          <t>https://www.indeed.com/viewjob?jk=941ac528d3de9bd2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Azure Data Engineer with Databricks</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Denver, CO, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a650bae5ce2865af</t>
+          <t>https://www.indeed.com/viewjob?jk=0696223bbad4f3b2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, USA USA</t>
+          <t>Brentwood, TN, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,24 +1044,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1830ef2a37b276</t>
+          <t>https://www.indeed.com/viewjob?jk=52c9a93606e8b426</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr. Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b919d7fa31ebc26</t>
+          <t>https://www.indeed.com/viewjob?jk=a650bae5ce2865af</t>
         </is>
       </c>
     </row>
@@ -1121,17 +1121,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shift4</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>Schaumburg, IL, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, Polars, Snowflake, Time Travel, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d034225cfcd8edfb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1830ef2a37b276</t>
         </is>
       </c>
     </row>
@@ -1191,25 +1191,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B2/C1 - AI Engineer 4</t>
+          <t>Embedded Software Architect – Safety product</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inspire uplift360</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d91279c1d35293f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdd6f4111720bf0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Scale Marketing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,34 +1244,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Lake Storage, Snowflake, Time Travel, Zero-Copy Cloning, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Kinesis, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99485071e09ba5d9</t>
+          <t>https://www.indeed.com/viewjob?jk=691cad96e500ec86</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer I (Data Pipelines)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sterling, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbfc9f6705769bd</t>
+          <t>https://www.indeed.com/viewjob?jk=77f88462ba46b951</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I (Data Pipelines)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f88462ba46b951</t>
+          <t>https://www.indeed.com/viewjob?jk=7aec8d989d23632c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>B2/C1 - AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,24 +1349,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aec8d989d23632c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e428958ad9e8a14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Data Lake Storage, Snowflake, Time Travel, Zero-Copy Cloning, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eca95f7972c478d</t>
+          <t>https://www.indeed.com/viewjob?jk=e186575a9835876a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B2/C1 - AI Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nightwing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Sterling, VA, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,42 +1419,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e428958ad9e8a14</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbfc9f6705769bd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Seattle)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ef35c3d0ab2f06</t>
+          <t>https://www.indeed.com/viewjob?jk=3eca95f7972c478d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - AI &amp; Cloud Platforms</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Staritas</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc03dc2d2fb3968d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5673baac86fbad3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Salt Lake City, UT, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,34 +1524,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d4e3867310a550</t>
+          <t>https://www.indeed.com/viewjob?jk=8f86cef93b901eda</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETDP Associate - Data Analytics</t>
+          <t>Senior Data Engineer (Seattle)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc612453c81627d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ef35c3d0ab2f06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Advisor-Data Engineer MDM</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FedEx Freight</t>
+          <t>Staritas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Memphis, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efe237925fb7924c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc03dc2d2fb3968d</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1646,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ETL Engineer - Hybrid (Atlanta, GA)</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,34 +1664,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f025291341db017</t>
+          <t>https://www.indeed.com/viewjob?jk=63d4e3867310a550</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>ETDP Associate - Data Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,34 +1699,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0631f3e16004ff9</t>
+          <t>https://www.indeed.com/viewjob?jk=cc612453c81627d3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>ETL Engineer - Hybrid (Atlanta, GA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,34 +1734,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f563024b3edfa1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f025291341db017</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>WorkWave™</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,34 +1769,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d8be6b3de911a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e0631f3e16004ff9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – ReactJS / Python / SQL Server</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Foresight IT</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S3, API Gateway, Azure, Scala, SQL Server, Data Modeling, REST API integration, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,24 +1814,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab9dc0adc464b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f563024b3edfa1e7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Developer II - Data Scientist</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wet Coast Logistics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Greenville, SC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, ETL, Power BI, MLOps, MLflow, pytest</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,24 +1849,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930ffb452c6e901</t>
+          <t>https://www.indeed.com/viewjob?jk=76d8be6b3de911a3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Quality Engineer - E2E Testing</t>
+          <t>Full Stack Engineer – ReactJS / Python / SQL Server</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Foresight IT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>S3, API Gateway, Azure, Scala, SQL Server, Data Modeling, REST API integration, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f74b13b92fba8065</t>
+          <t>https://www.indeed.com/viewjob?jk=03ab9dc0adc464b1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Development Security Operations (DevSecOps) Engineer</t>
+          <t>Data &amp; Analytics Developer II - Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AEG Worldwide</t>
+          <t>Wet Coast Logistics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Greenville, SC, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,42 +1909,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, ETL, Power BI, MLOps, MLflow, pytest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1e4327cd6468ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4930ffb452c6e901</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Engineer - E2E Testing</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,59 +1954,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b039efd1bdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=f74b13b92fba8065</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Development Security Operations (DevSecOps) Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Naviga Inc.</t>
+          <t>AEG Worldwide</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2a21fac0f0100e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1e4327cd6468ba</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Engineer, Data Services</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Curant Health Georgia LLC</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Smyrna, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,34 +2014,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f2fb1b8f4b0f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=51dae1964caf1fbb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Services</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Tampa, FL, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dae1964caf1fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=abce2386bdc64e52</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,29 +2084,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abce2386bdc64e52</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b039efd1bdf1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Developer III</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BAM Technologies, LLC</t>
+          <t>Naviga Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b4ba48e48f905c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2a21fac0f0100e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Python Developer w/d banking domain Exp in Jersey City, NJ – 5 Days Onsite</t>
+          <t>Full Stack Developer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SGN Global Technologies</t>
+          <t>BAM Technologies, LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e855da5922ac48</t>
+          <t>https://www.indeed.com/viewjob?jk=12b4ba48e48f905c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Python Developer w/d banking domain Exp in Jersey City, NJ – 5 Days Onsite</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>SGN Global Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Jersey City, NJ, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,34 +2189,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b69cb4c0ab9836b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e855da5922ac48</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Architect (AWS)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Norfolk Southern</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,24 +2234,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=014160cc6df2ce6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b69cb4c0ab9836b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI/ML DevOps Engineer</t>
+          <t>Enterprise Cloud Architect (AWS)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Norfolk Southern</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,32 +2269,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fcf0f91468d631</t>
+          <t>https://www.indeed.com/viewjob?jk=014160cc6df2ce6d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, React, AWS)</t>
+          <t>AI/ML DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cambridge, MA, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,14 +2304,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62a73708df2af64b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fcf0f91468d631</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python/AWS)</t>
+          <t>Full-Stack Engineer 4 (Python, React, AWS)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f16cbf818d2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=62a73708df2af64b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full-stack Engineer 4 (Python/AWS)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Westminster, CO, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,34 +2364,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0440d6698d77fe</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f16cbf818d2cc7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>Westminster, CO, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2cfdc750e170ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0440d6698d77fe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer-Xumo</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Mountain View, CA, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Spark, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d075be1566febf4</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2cfdc750e170ad</t>
         </is>
       </c>
     </row>
@@ -2626,17 +2626,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer-Application Security Tooling (SCA/SAST/ DAST/ MAST/ API Security)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ed5a614020b926</t>
+          <t>https://www.indeed.com/viewjob?jk=2896efcf20f6d63a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Cyber Security Engineer-Application Security Tooling (SCA/SAST/ DAST/ MAST/ API Security)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,69 +2679,69 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e910c2a9db14c45</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ed5a614020b926</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Milpitas, CA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, YARN, Scala, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb578f07aff6f110</t>
+          <t>https://www.indeed.com/viewjob?jk=3e910c2a9db14c45</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, USA USA</t>
+          <t>Milpitas, CA, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, YARN, Scala, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145ea1e85469e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb578f07aff6f110</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Willow Grove, PA, USA USA</t>
+          <t>Newport Beach, CA, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113b0ef7bbd43b1b</t>
+          <t>https://www.indeed.com/viewjob?jk=145ea1e85469e08e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer ( Contract -Corp to Corp)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>AZ TECHNOLOGY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lemont, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,24 +2829,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c58980479804216</t>
+          <t>https://www.indeed.com/viewjob?jk=2ebb8d2fdac54e89</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, USA USA</t>
+          <t>Lemont, IL, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d377e0f22b50c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c58980479804216</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Liberty company insurance brokers</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, USA USA</t>
+          <t>Oklahoma City, OK, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,24 +2899,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cea5cc81a279b30</t>
+          <t>https://www.indeed.com/viewjob?jk=03d377e0f22b50c9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Enable Dental</t>
+          <t>Liberty company insurance brokers</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Woodland Hills, CA, USA USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,24 +2934,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b35f71127e713c</t>
+          <t>https://www.indeed.com/viewjob?jk=6cea5cc81a279b30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Surge InfoTech LLC</t>
+          <t>12 Elements Consulting</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Alexandria, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,24 +2969,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009031cd529e79e4</t>
+          <t>https://www.indeed.com/viewjob?jk=961c09494cecca9b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12 Elements Consulting</t>
+          <t>Enable Dental</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961c09494cecca9b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b35f71127e713c</t>
         </is>
       </c>
     </row>
@@ -3116,17 +3116,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
+          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Miami, FL, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3144,24 +3144,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b64e32ec1fb240</t>
+          <t>https://www.indeed.com/viewjob?jk=68f0e55cdb56404f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Reston, VA, USA USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+          <t>RDS, Azure, Databricks, Scala, ELT, MLOps, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3179,24 +3179,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f0e55cdb56404f</t>
+          <t>https://www.indeed.com/viewjob?jk=96a354be84c2774c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>.NET / PostgreSQL Full Stack Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,34 +3204,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, ELT, MLOps, MLflow, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, S3, Scala, PostgreSQL, ETL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a354be84c2774c</t>
+          <t>https://www.indeed.com/viewjob?jk=4942ca1d88558983</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>.NET / PostgreSQL Full Stack Developer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Strategic Operational Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Washington, DC, USA USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,34 +3239,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, PostgreSQL, ETL, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4942ca1d88558983</t>
+          <t>https://www.indeed.com/viewjob?jk=aa47a8ff9ab65e1a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Automation Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Strategic Operational Solutions</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Santa Ana, CA, USA USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,50 +3274,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa47a8ff9ab65e1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Automation Developer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Orange County's Credit Union</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Santa Ana, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed32f5ec4264db1b</t>
         </is>

--- a/results/job_matches_2026-10-09.xlsx
+++ b/results/job_matches_2026-10-09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,52 +456,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Validation Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb22b319ea013fb</t>
+          <t>https://www.indeed.com/viewjob?jk=00fea8871f48cca2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Software Engineer I - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,24 +519,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dc6eea200704fa</t>
+          <t>https://www.indeed.com/viewjob?jk=caff522a25e0d7d6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Magento Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,42 +544,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a263552cfd74efb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b8dc6eea200704fa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Senior Magento Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0aa6dd1b04fbce5</t>
+          <t>https://www.indeed.com/viewjob?jk=a263552cfd74efb4</t>
         </is>
       </c>
     </row>
@@ -631,17 +631,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data and Analytics Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, USA USA</t>
+          <t>Brookfield, WI, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -649,34 +649,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ecc8f399660dece</t>
+          <t>https://www.indeed.com/viewjob?jk=105449350f0e9ec0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>IT Data Analytics Specialist - Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westlake, TX, USA USA</t>
+          <t>Westerville, OH, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,34 +684,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Oracle, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90944751a08861f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1f3467fcbde954</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Westlake, TX, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,32 +729,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803b407aed33b34c</t>
+          <t>https://www.indeed.com/viewjob?jk=c90944751a08861f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B1 - AI Platform Engineer - Agentic AI</t>
+          <t>Snowflake DBA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CLOUDSCOUTS SOFTWARE SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Time Travel, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26f6d29c9750839</t>
+          <t>https://www.indeed.com/viewjob?jk=f220289c65db145a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kansas City, MO, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a2d2e8f143d7289</t>
+          <t>https://www.indeed.com/viewjob?jk=803b407aed33b34c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Platforms - REMOTE</t>
+          <t>Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fortified Data</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73378029918e0cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb9d612ea54d97c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>B1 - AI Platform Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hialeah, FL, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Oracle, Data Modeling, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,24 +869,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecf219ffd88edd6e</t>
+          <t>https://www.indeed.com/viewjob?jk=a26f6d29c9750839</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FTS Network Services – Data Analytics Advisor</t>
+          <t>Senior Consultant - Data Platforms - REMOTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Fortified Data</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,24 +904,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39867fe787e05360</t>
+          <t>https://www.indeed.com/viewjob?jk=73378029918e0cc3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oaks, PA, USA USA</t>
+          <t>Hialeah, FL, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -929,34 +929,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Oracle, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8210b0e233986964</t>
+          <t>https://www.indeed.com/viewjob?jk=ecf219ffd88edd6e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>FTS Network Services – Data Analytics Advisor</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irvine, CA, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -964,34 +964,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941ac528d3de9bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=39867fe787e05360</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Oaks, PA, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,69 +999,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0696223bbad4f3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8210b0e233986964</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brentwood, TN, USA USA</t>
+          <t>Denver, CO, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c9a93606e8b426</t>
+          <t>https://www.indeed.com/viewjob?jk=0696223bbad4f3b2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Azure Data Engineer with Databricks</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1069,34 +1069,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a650bae5ce2865af</t>
+          <t>https://www.indeed.com/viewjob?jk=177df3e8e3426cf7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Engineering - Software Engineer II - P2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shift4</t>
+          <t>Credit One Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,24 +1104,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, Polars, Snowflake, Time Travel, dbt, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6edb1d735ef07e</t>
+          <t>https://www.indeed.com/viewjob?jk=2de03d7d6acc99ef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, USA USA</t>
+          <t>Brentwood, TN, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1830ef2a37b276</t>
+          <t>https://www.indeed.com/viewjob?jk=52c9a93606e8b426</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Azure Data Engineer with Databricks</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alvaria</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Philadelphia, PA, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb0737b251a7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=a650bae5ce2865af</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Embedded Software Architect – Safety product</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Inspire uplift360</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Schaumburg, IL, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,104 +1209,104 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdd6f4111720bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a1830ef2a37b276</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Scale Marketing</t>
+          <t>Alvaria</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>TX, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691cad96e500ec86</t>
+          <t>https://www.indeed.com/viewjob?jk=6cb0737b251a7eee</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I (Data Pipelines)</t>
+          <t>Embedded Software Architect – Safety product</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Inspire uplift360</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Hive, Scala, PostgreSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f88462ba46b951</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdd6f4111720bf0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Dayton, OH, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aec8d989d23632c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b54828a79f2eaef</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B2/C1 - AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scale Marketing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,24 +1359,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e428958ad9e8a14</t>
+          <t>https://www.indeed.com/viewjob?jk=691cad96e500ec86</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>B2/C1 - AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,34 +1384,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Lake Storage, Snowflake, Time Travel, Zero-Copy Cloning, Data Modeling, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e186575a9835876a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e428958ad9e8a14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nightwing</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sterling, VA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Data Lake Storage, Snowflake, Time Travel, Zero-Copy Cloning, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbfc9f6705769bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e186575a9835876a</t>
         </is>
       </c>
     </row>
@@ -1471,17 +1471,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI &amp; Cloud Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>T prods solutions inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5673baac86fbad3</t>
+          <t>https://www.indeed.com/viewjob?jk=472e078ffbc1788b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Davide Dev Technology &amp; Software Solutions LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,54 +1534,54 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f86cef93b901eda</t>
+          <t>https://www.indeed.com/viewjob?jk=95518c1035c2ad36</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Seattle)</t>
+          <t>Senior Software Engineer - AI &amp; Cloud Platforms</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ef35c3d0ab2f06</t>
+          <t>https://www.indeed.com/viewjob?jk=f5673baac86fbad3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Machine Learning Engineering Sr -</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Staritas</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1590,11 +1590,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, ETL</t>
+          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,94 +1604,94 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc03dc2d2fb3968d</t>
+          <t>https://www.indeed.com/viewjob?jk=25e732a62993b114</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>sdfsd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Zacki's Culinary Creations</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Byhalia, MS, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e322091c12151da</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4582166f5e7749</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ICF</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Reston, VA, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Kafka, Oracle, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d4e3867310a550</t>
+          <t>https://www.indeed.com/viewjob?jk=34ebb49cffa42b9e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ETDP Associate - Data Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>Salt Lake City, UT, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,34 +1699,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc612453c81627d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f86cef93b901eda</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETL Engineer - Hybrid (Atlanta, GA)</t>
+          <t>Senior Data Engineer (Seattle)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Seattle, WA, USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,34 +1734,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, ETL, dbt, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f025291341db017</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ef35c3d0ab2f06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,29 +1769,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0631f3e16004ff9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e322091c12151da</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1804,34 +1804,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f563024b3edfa1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=313a5f9d6a0de5e3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,34 +1839,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Spark, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d8be6b3de911a3</t>
+          <t>https://www.indeed.com/viewjob?jk=278357c0443f7d7f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – ReactJS / Python / SQL Server</t>
+          <t>ETL Engineer - Hybrid (Atlanta, GA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Foresight IT</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,34 +1874,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S3, API Gateway, Azure, Scala, SQL Server, Data Modeling, REST API integration, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ab9dc0adc464b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f025291341db017</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Developer II - Data Scientist</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wet Coast Logistics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Greenville, SC, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, ETL, Power BI, MLOps, MLflow, pytest</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930ffb452c6e901</t>
+          <t>https://www.indeed.com/viewjob?jk=f563024b3edfa1e7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Quality Engineer - E2E Testing</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f74b13b92fba8065</t>
+          <t>https://www.indeed.com/viewjob?jk=76d8be6b3de911a3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Development Security Operations (DevSecOps) Engineer</t>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; AI Platform</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AEG Worldwide</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,67 +1989,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1e4327cd6468ba</t>
+          <t>https://www.indeed.com/viewjob?jk=04eb3364f452214e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Services</t>
+          <t>Quality Engineer - E2E Testing</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dae1964caf1fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=f74b13b92fba8065</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Development Security Operations (DevSecOps) Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>AEG Worldwide</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, USA USA</t>
+          <t>Los Angeles, CA, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abce2386bdc64e52</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1e4327cd6468ba</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer, Data Services</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>TrueML</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b039efd1bdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=51dae1964caf1fbb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Naviga Inc.</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2a21fac0f0100e</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b039efd1bdf1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Developer III</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BAM Technologies, LLC</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Aurora, CO, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,34 +2154,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12b4ba48e48f905c</t>
+          <t>https://www.indeed.com/viewjob?jk=8246359c72573dc5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Python Developer w/d banking domain Exp in Jersey City, NJ – 5 Days Onsite</t>
+          <t>Azure Cloud Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SGN Global Technologies</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, USA USA</t>
+          <t>Cleveland, OH, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e855da5922ac48</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6069a1656fe1c8</t>
         </is>
       </c>
     </row>
@@ -2311,17 +2311,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, React, AWS)</t>
+          <t>Analyst, Data Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cambridge, MA, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Step Functions, S3, SQS, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,14 +2339,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62a73708df2af64b</t>
+          <t>https://www.indeed.com/viewjob?jk=35e14c9c697d2f12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python/AWS)</t>
+          <t>Full-Stack Engineer 4 (Python, React, AWS)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f16cbf818d2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=62a73708df2af64b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full-stack Engineer 4 (Python/AWS)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westminster, CO, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,34 +2399,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0440d6698d77fe</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f16cbf818d2cc7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA USA</t>
+          <t>Westminster, CO, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2cfdc750e170ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0440d6698d77fe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mid-Level Snowflake Developer</t>
+          <t>Sr. Python Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>GA, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,34 +2469,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Cloud Storage, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa77e320b69a5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9491761135bfafe3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Platforms</t>
+          <t>Mid-Level Snowflake Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Cloud Storage, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,24 +2514,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10cdbcee7e892fd</t>
+          <t>https://www.indeed.com/viewjob?jk=efa77e320b69a5d6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure Databricks architect</t>
+          <t>Software Engineer, Core Platforms</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RM SOLUTIONS INC</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Houston, TX, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,19 +2549,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d787c2acfd2551</t>
+          <t>https://www.indeed.com/viewjob?jk=c10cdbcee7e892fd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mindbody</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, SQL Server, PostgreSQL, MongoDB, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Power BI, Tableau, MLOps, MLflow, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,19 +2584,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f824146c3510fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a11006b13bb999b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Customer Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Harness</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2609,34 +2609,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Power BI, Tableau, MLOps, MLflow, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a11006b13bb999b</t>
+          <t>https://www.indeed.com/viewjob?jk=26cf45d0f7cb82c9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cyber Security Engineer-Application Security Tooling (SCA/SAST/ DAST/ MAST/ API Security)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2896efcf20f6d63a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ed5a614020b926</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer-Application Security Tooling (SCA/SAST/ DAST/ MAST/ API Security)</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,34 +2679,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ed5a614020b926</t>
+          <t>https://www.indeed.com/viewjob?jk=3e910c2a9db14c45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,42 +2714,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e910c2a9db14c45</t>
+          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Milpitas, CA, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, YARN, Scala, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,24 +2759,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb578f07aff6f110</t>
+          <t>https://www.indeed.com/viewjob?jk=2896efcf20f6d63a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,34 +2784,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145ea1e85469e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer ( Contract -Corp to Corp)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AZ TECHNOLOGY</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Milpitas, CA, USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, S3, ECS, YARN, Scala, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,24 +2829,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ebb8d2fdac54e89</t>
+          <t>https://www.indeed.com/viewjob?jk=eb578f07aff6f110</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lemont, IL, USA USA</t>
+          <t>Newport Beach, CA, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c58980479804216</t>
+          <t>https://www.indeed.com/viewjob?jk=145ea1e85469e08e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer ( Contract -Corp to Corp)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>AZ TECHNOLOGY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,34 +2889,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Redshift, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03d377e0f22b50c9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ebb8d2fdac54e89</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Cloud Engineer, AI- Enabled Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Liberty company insurance brokers</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, USA USA</t>
+          <t>Lemont, IL, USA USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,34 +2924,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, SQL Server, ETL, ELT, Tableau, Terraform, Git, Azure Monitor</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cea5cc81a279b30</t>
+          <t>https://www.indeed.com/viewjob?jk=0c58980479804216</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12 Elements Consulting</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Oklahoma City, OK, USA USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, ETL, ELT</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,24 +2969,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961c09494cecca9b</t>
+          <t>https://www.indeed.com/viewjob?jk=03d377e0f22b50c9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Enable Dental</t>
+          <t>Radinnova</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2994,17 +2994,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Dataflow, Spark, PySpark, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b35f71127e713c</t>
+          <t>https://www.indeed.com/viewjob?jk=504153bebacded2e</t>
         </is>
       </c>
     </row>
@@ -3081,17 +3081,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enterprise Software Engineer II</t>
+          <t>.NET / PostgreSQL Full Stack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dartmouth College</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hanover, NH, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3099,24 +3099,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, Scala, PostgreSQL, ETL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147e1a8f49587d0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4942ca1d88558983</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business, Named Accounts</t>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; AI Platform</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3134,17 +3134,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f0e55cdb56404f</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ef033d6bdd0980</t>
         </is>
       </c>
     </row>
@@ -3186,17 +3186,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>.NET / PostgreSQL Full Stack Developer</t>
+          <t>Senior Automation Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Santa Ana, CA, USA USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, PostgreSQL, ETL, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3213,76 +3213,6 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4942ca1d88558983</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Database Administrator</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Strategic Operational Solutions</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Washington, DC, USA USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa47a8ff9ab65e1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Automation Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Orange County's Credit Union</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Santa Ana, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed32f5ec4264db1b</t>
         </is>

--- a/results/job_matches_2026-10-09.xlsx
+++ b/results/job_matches_2026-10-09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,25 +491,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Enterprise Architecture</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,24 +519,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caff522a25e0d7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1716679382a11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Software Engineer I - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,24 +554,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8dc6eea200704fa</t>
+          <t>https://www.indeed.com/viewjob?jk=caff522a25e0d7d6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Magento Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Irving, TX, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -579,77 +579,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Scala, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a263552cfd74efb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b8dc6eea200704fa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data and Analytics Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alvaria</t>
+          <t>SysLogic, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Brookfield, WI, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, API Gateway, IAM, RDS, Azure, GCP</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39485b7b1b648afd</t>
+          <t>https://www.indeed.com/viewjob?jk=105449350f0e9ec0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect - MS Fabric</t>
+          <t>IT Data Analytics Specialist - Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brookfield, WI, USA USA</t>
+          <t>Westerville, OH, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Oracle, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,24 +659,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105449350f0e9ec0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1f3467fcbde954</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT Data Analytics Specialist - Data Engineer</t>
+          <t>Snowflake DBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>CLOUDSCOUTS SOFTWARE SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westerville, OH, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Kafka, Snowflake, Oracle, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Time Travel, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1f3467fcbde954</t>
+          <t>https://www.indeed.com/viewjob?jk=f220289c65db145a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Specialist - Software Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Westlake, TX, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -719,42 +719,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Spark, Kafka, Snowflake</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90944751a08861f</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb9d612ea54d97c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Snowflake DBA</t>
+          <t>B1 - AI Platform Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CLOUDSCOUTS SOFTWARE SOLUTIONS LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Time Travel, Dimensional Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,67 +764,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f220289c65db145a</t>
+          <t>https://www.indeed.com/viewjob?jk=a26f6d29c9750839</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Consultant - Data Platforms - REMOTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fortified Data</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Raleigh, NC, USA USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803b407aed33b34c</t>
+          <t>https://www.indeed.com/viewjob?jk=73378029918e0cc3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Hialeah, FL, USA USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Oracle, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb9d612ea54d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=ecf219ffd88edd6e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B1 - AI Platform Engineer - Agentic AI</t>
+          <t>MDM Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>Denver, CO, USA USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26f6d29c9750839</t>
+          <t>https://www.indeed.com/viewjob?jk=0696223bbad4f3b2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Platforms - REMOTE</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fortified Data</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>Plano, TX, USA USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73378029918e0cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=177df3e8e3426cf7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Observability Engineer (Splunk / SignalFx) - US Citizen or Green Card only</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Nextiya</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hialeah, FL, USA USA</t>
+          <t>Fairfax, VA, USA USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Oracle, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecf219ffd88edd6e</t>
+          <t>https://www.indeed.com/viewjob?jk=653c3efd16cc3edd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FTS Network Services – Data Analytics Advisor</t>
+          <t>Enterprise Data Engineering - Software Engineer II - P2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Credit One Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, USA USA</t>
+          <t>Las Vegas, NV, USA USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,67 +974,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39867fe787e05360</t>
+          <t>https://www.indeed.com/viewjob?jk=2de03d7d6acc99ef</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Database Analysis - Advisor II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oaks, PA, USA USA</t>
+          <t>Berkeley Heights, NJ, USA USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8210b0e233986964</t>
+          <t>https://www.indeed.com/viewjob?jk=c172f0ee95b96be9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MDM Architect</t>
+          <t>ETL Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Huntsman Cancer Institute</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, USA USA</t>
+          <t>Salt Lake City, UT, USA USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,32 +1044,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0696223bbad4f3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d07fe5896fdd369</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, USA USA</t>
+          <t>Dayton, OH, USA USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Cloud Storage, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
+          <t>Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177df3e8e3426cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b54828a79f2eaef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineering - Software Engineer II - P2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Credit One Bank</t>
+          <t>Scale Marketing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, USA USA</t>
+          <t>Chicago, IL, USA USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,102 +1114,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de03d7d6acc99ef</t>
+          <t>https://www.indeed.com/viewjob?jk=691cad96e500ec86</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brentwood, TN, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c9a93606e8b426</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b6ccb1a0a82581</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Azure Data Engineer with Databricks</t>
+          <t>B2/C1 - AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, USA USA</t>
+          <t>Charlotte, NC, USA USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a650bae5ce2865af</t>
+          <t>https://www.indeed.com/viewjob?jk=9e428958ad9e8a14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Snowflake Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Lake Storage, Snowflake, Time Travel, Zero-Copy Cloning, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,102 +1219,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1830ef2a37b276</t>
+          <t>https://www.indeed.com/viewjob?jk=e186575a9835876a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>. NET Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alvaria</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, USA USA</t>
+          <t>Denver, CO, USA USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, GCP, Scala, MongoDB, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, SQL Server, Kimball, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cb0737b251a7eee</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf663ec36e61e57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Embedded Software Architect – Safety product</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Inspire uplift360</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdd6f4111720bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=3eca95f7972c478d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>T prods solutions inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dayton, OH, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,32 +1324,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b54828a79f2eaef</t>
+          <t>https://www.indeed.com/viewjob?jk=472e078ffbc1788b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Scale Marketing</t>
+          <t>Davide Dev Technology &amp; Software Solutions LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691cad96e500ec86</t>
+          <t>https://www.indeed.com/viewjob?jk=95518c1035c2ad36</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B2/C1 - AI Engineer</t>
+          <t>Neural Network Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Precision CastParts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Oracle, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e428958ad9e8a14</t>
+          <t>https://www.indeed.com/viewjob?jk=d09d3af3922e9dae</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Snowflake Developer</t>
+          <t>AI Machine Learning Engineering Sr -</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1415,73 +1415,73 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Lake Storage, Snowflake, Time Travel, Zero-Copy Cloning, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e186575a9835876a</t>
+          <t>https://www.indeed.com/viewjob?jk=25e732a62993b114</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Pittsburgh, PA, USA USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Kafka, Oracle, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eca95f7972c478d</t>
+          <t>https://www.indeed.com/viewjob?jk=34ebb49cffa42b9e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>sdfsd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>T prods solutions inc</t>
+          <t>Zacki's Culinary Creations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Byhalia, MS, USA USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,32 +1499,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472e078ffbc1788b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d4582166f5e7749</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Davide Dev Technology &amp; Software Solutions LLC</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>Salt Lake City, UT, USA USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,32 +1534,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95518c1035c2ad36</t>
+          <t>https://www.indeed.com/viewjob?jk=8f86cef93b901eda</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI &amp; Cloud Platforms</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,32 +1569,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5673baac86fbad3</t>
+          <t>https://www.indeed.com/viewjob?jk=07e10edc2fd4bcbe</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineering Sr -</t>
+          <t>AI, Data &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>QualDerm Partners LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Brentwood, TN, USA USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Spark, Spark Streaming, Kafka, PostgreSQL, MySQL, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Streams/Tasks, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,32 +1604,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25e732a62993b114</t>
+          <t>https://www.indeed.com/viewjob?jk=150bee16d3bf5873</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sdfsd</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zacki's Culinary Creations</t>
+          <t>Encoura</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Byhalia, MS, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,32 +1639,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d4582166f5e7749</t>
+          <t>https://www.indeed.com/viewjob?jk=313a5f9d6a0de5e3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Kafka, Oracle, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Spark, Scala, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ebb49cffa42b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=278357c0443f7d7f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Engineer - Hybrid (Atlanta, GA)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Hive, Impala, Spark, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f86cef93b901eda</t>
+          <t>https://www.indeed.com/viewjob?jk=7f025291341db017</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Seattle)</t>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; AI Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,77 +1734,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ef35c3d0ab2f06</t>
+          <t>https://www.indeed.com/viewjob?jk=04eb3364f452214e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Aurora, CO, USA USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e322091c12151da</t>
+          <t>https://www.indeed.com/viewjob?jk=8246359c72573dc5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Azure Cloud Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Encoura</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Cleveland, OH, USA USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, Scala, SQL Server, PostgreSQL, MongoDB, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1814,32 +1814,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=313a5f9d6a0de5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6069a1656fe1c8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Data Masking Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Spark, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1849,32 +1849,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278357c0443f7d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba50192afaa67e55</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ETL Engineer - Hybrid (Atlanta, GA)</t>
+          <t>Automation Engineer - Platform Integration (Contract)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>Allied Universal Electronic Monitoring</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Snowflake, SQL Server, ETL, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,102 +1884,102 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f025291341db017</t>
+          <t>https://www.indeed.com/viewjob?jk=c966893b82682957</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Hoboken, NJ, USA USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f563024b3edfa1e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb450772af81f1d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d8be6b3de911a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3b69cb4c0ab9836b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - AWS Infrastructure &amp; AI Platform</t>
+          <t>Enterprise Cloud Architect (AWS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Norfolk Southern</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA USA</t>
+          <t>Atlanta, GA, USA USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,67 +1989,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eb3364f452214e</t>
+          <t>https://www.indeed.com/viewjob?jk=014160cc6df2ce6d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Quality Engineer - E2E Testing</t>
+          <t>AI/ML DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA USA</t>
+          <t>Austin, TX, USA USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f74b13b92fba8065</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fcf0f91468d631</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Development Security Operations (DevSecOps) Engineer</t>
+          <t>Analyst, Data Engineer, Firehouse Subs</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AEG Worldwide</t>
+          <t>Firehouse Subs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA USA</t>
+          <t>Jacksonville, FL, USA USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Splunk, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Step Functions, S3, SQS, RDS, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,32 +2059,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1e4327cd6468ba</t>
+          <t>https://www.indeed.com/viewjob?jk=35e14c9c697d2f12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Services</t>
+          <t>Full-Stack Engineer 4 (Python, React, AWS)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TrueML</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,67 +2094,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51dae1964caf1fbb</t>
+          <t>https://www.indeed.com/viewjob?jk=62a73708df2af64b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4 (Python/AWS)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Cambridge, MA, USA USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b039efd1bdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f16cbf818d2cc7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>FinOps Engineer, Cloud &amp; Kubernetes Optimization</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Aurora, CO, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Dataflow, Scala, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, ELT, Power BI, Tableau, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,32 +2164,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246359c72573dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9733fdbf85f59250</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer II</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cleveland, OH, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,32 +2199,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6069a1656fe1c8</t>
+          <t>https://www.indeed.com/viewjob?jk=771ada10ea70766c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Python Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, USA USA</t>
+          <t>GA, USA USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,94 +2234,94 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b69cb4c0ab9836b</t>
+          <t>https://www.indeed.com/viewjob?jk=9491761135bfafe3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Architect (AWS)</t>
+          <t>Mid-Level Snowflake Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Norfolk Southern</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Cloud Storage, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=014160cc6df2ce6d</t>
+          <t>https://www.indeed.com/viewjob?jk=efa77e320b69a5d6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI/ML DevOps Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Power BI, Tableau, MLOps, MLflow, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fcf0f91468d631</t>
+          <t>https://www.indeed.com/viewjob?jk=7a11006b13bb999b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analyst, Data Engineer, Firehouse Subs</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Firehouse Subs</t>
+          <t>Pursuit Aerospace</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, S3, SQS, RDS, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e14c9c697d2f12</t>
+          <t>https://www.indeed.com/viewjob?jk=afd8d15d41de082d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Python, React, AWS)</t>
+          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cambridge, MA, USA USA</t>
+          <t>New York, NY, USA USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62a73708df2af64b</t>
+          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Python/AWS)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cambridge, MA, USA USA</t>
+          <t>Boise, ID, USA USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3f16cbf818d2cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=2896efcf20f6d63a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI - Software Engineering-Sr Professional I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Westminster, CO, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,34 +2434,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Cloud Storage, Vertex AI, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0440d6698d77fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7126fa6216c927d2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Python Data Engineer</t>
+          <t>AI - Software Engineering Advisor I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, USA USA</t>
+          <t>Alpharetta, GA, USA USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Scala, Kafka, Snowflake, SQL Server, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,19 +2479,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9491761135bfafe3</t>
+          <t>https://www.indeed.com/viewjob?jk=b29d0fe789c8060e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mid-Level Snowflake Developer</t>
+          <t>Senior Customer Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Harness</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2504,34 +2504,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Cloud Storage, Snowflake, Data Modeling, ELT, dbt, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa77e320b69a5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=26cf45d0f7cb82c9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Platforms</t>
+          <t>Cyber Security Engineer-Application Security Tooling (SCA/SAST/ DAST/ MAST/ API Security)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bot Auto</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, USA USA</t>
+          <t>Phoenix, AZ, USA USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,77 +2539,77 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10cdbcee7e892fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ed5a614020b926</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Dallas, TX, USA USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Power BI, Tableau, MLOps, MLflow, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a11006b13bb999b</t>
+          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Customer Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Harness</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Milpitas, CA, USA USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, YARN, Scala, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cf45d0f7cb82c9</t>
+          <t>https://www.indeed.com/viewjob?jk=eb578f07aff6f110</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cyber Security Engineer-Application Security Tooling (SCA/SAST/ DAST/ MAST/ API Security)</t>
+          <t>Data Engineer ( Contract -Corp to Corp)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>AZ TECHNOLOGY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Oracle, PostgreSQL, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>Redshift, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,67 +2654,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ed5a614020b926</t>
+          <t>https://www.indeed.com/viewjob?jk=2ebb8d2fdac54e89</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Lemont, IL, USA USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e910c2a9db14c45</t>
+          <t>https://www.indeed.com/viewjob?jk=0c58980479804216</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Financial Services - Forward Deployed Engineer - Technology Consulting - Senior - NYC</t>
+          <t>Senior Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Radinnova</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Vertex AI, Scala, Docker, Kubernetes, AKS, Git</t>
+          <t>Azure, Data Factory, Dataflow, Spark, PySpark, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aa91fe9a6b8f53</t>
+          <t>https://www.indeed.com/viewjob?jk=504153bebacded2e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boise, ID, USA USA</t>
+          <t>Research Triangle Park, NC, USA USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Snowflake, Oracle, MongoDB, NoSQL, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2759,24 +2759,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2896efcf20f6d63a</t>
+          <t>https://www.indeed.com/viewjob?jk=703acd54a03be894</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Platform Engineer</t>
+          <t>.NET / PostgreSQL Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, Scala, PostgreSQL, ETL, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fb867bcabb2d1a</t>
+          <t>https://www.indeed.com/viewjob?jk=4942ca1d88558983</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; AI Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Milpitas, CA, USA USA</t>
+          <t>USA USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, YARN, Scala, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,24 +2829,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb578f07aff6f110</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ef033d6bdd0980</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Care Access</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, USA USA</t>
+          <t>Boston, MA, USA USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Athena, RDS, Scala, dbt, MLOps, CI/CD, Docker, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145ea1e85469e08e</t>
+          <t>https://www.indeed.com/viewjob?jk=54af70793b1dd612</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer ( Contract -Corp to Corp)</t>
+          <t>Senior Automation Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AZ TECHNOLOGY</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Santa Ana, CA, USA USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2898,321 +2898,6 @@
         </is>
       </c>
       <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ebb8d2fdac54e89</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Argonne National Laboratory</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Lemont, IL, USA USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c58980479804216</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CFS Brands, LLC</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, USA USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03d377e0f22b50c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Microsoft Fabric Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Radinnova</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Dataflow, Spark, PySpark, SQL Server, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=504153bebacded2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, USA USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Snowflake, Oracle, MongoDB, NoSQL, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=703acd54a03be894</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer II</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Medpro systems</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Mount Arlington, NJ, USA USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MongoDB, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4711747a7e234c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>.NET / PostgreSQL Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, Scala, PostgreSQL, ETL, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4942ca1d88558983</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Azure Infrastructure &amp; AI Platform</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ef033d6bdd0980</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Reston, VA, USA USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, ELT, MLOps, MLflow, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96a354be84c2774c</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Automation Developer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Orange County's Credit Union</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Santa Ana, CA, USA USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed32f5ec4264db1b</t>
         </is>
